--- a/tools/importer/reports/import-annual-report-performance.report.xlsx
+++ b/tools/importer/reports/import-annual-report-performance.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>_reportFile</t>
   </si>
@@ -49,7 +49,7 @@
     <t>annual-report-performance</t>
   </si>
   <si>
-    <t>2026-04-29T22:34:15.062Z</t>
+    <t>2026-04-30T21:02:09.231Z</t>
   </si>
   <si>
     <t>Performance Annual Report 2021 | EDC</t>
@@ -115,13 +115,16 @@
     <t>en/about-us/corporate/corporate-reports/2022-annual-report/performance</t>
   </si>
   <si>
-    <t>2026-04-29T18:03:31.040Z</t>
+    <t>2026-04-30T20:51:16.229Z</t>
   </si>
   <si>
     <t>Performance Annual Report 2022 | EDC</t>
   </si>
   <si>
     <t>https://www.edc.ca/en/about-us/corporate/corporate-reports/2022-annual-report/performance.html</t>
+  </si>
+  <si>
+    <t>[{"alt":"Split-screen image of a group of people having a meeting around a table (left) and a young Asian businesswoman looking ahead with  a smile, holding a smartphone (right).","desktop":"https://www.edc.ca/content/dam/edc/en/lifestyle/outdoor/performance-2022-hero-d.jpg","tablet":"https://www.edc.ca/content/dam/edc/en/lifestyle/indoor/2022-annual-report-4-t.jpg","mobile":"https://www.edc.ca/content/dam/edc/en/lifestyle/outdoor/performance-2022-hero-m.jpg","fallback":"https://www.edc.ca/content/dam/edc/en/lifestyle/outdoor/performance-2022-hero-m.jpg"},{"alt":"2023 climate target progress chart.","desktop":"https://www.edc.ca/content/dam/edc/en/infographics/performance-2022-7.jpg","tablet":"https://www.edc.ca/content/dam/edc/en/infographics/performance-2022-7.jpg","mobile":"https://www.edc.ca/content/dam/edc/en/infographics/performance-2022-7-m.jpg","fallback":"https://www.edc.ca/content/dam/edc/en/infographics/performance-2022-7-m.jpg"}]</t>
   </si>
 </sst>
 </file>
@@ -673,7 +676,7 @@
         <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-annual-report-performance.report.xlsx
+++ b/tools/importer/reports/import-annual-report-performance.report.xlsx
@@ -49,7 +49,7 @@
     <t>annual-report-performance</t>
   </si>
   <si>
-    <t>2026-04-30T21:02:09.231Z</t>
+    <t>2026-04-30T22:08:57.550Z</t>
   </si>
   <si>
     <t>Performance Annual Report 2021 | EDC</t>
@@ -115,7 +115,7 @@
     <t>en/about-us/corporate/corporate-reports/2022-annual-report/performance</t>
   </si>
   <si>
-    <t>2026-04-30T20:51:16.229Z</t>
+    <t>2026-04-30T21:56:15.862Z</t>
   </si>
   <si>
     <t>Performance Annual Report 2022 | EDC</t>
